--- a/docs/Requisitos - Delicia Gelada.xlsx
+++ b/docs/Requisitos - Delicia Gelada.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="155" uniqueCount="135">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="170" uniqueCount="146">
   <si>
     <t>Organização</t>
   </si>
@@ -76,6 +76,12 @@
     <t>Revisão dos Requisitos</t>
   </si>
   <si>
+    <t>Kauan Alves</t>
+  </si>
+  <si>
+    <t>Correção da Regra de Negócio</t>
+  </si>
+  <si>
     <t>Requisitos Técnicos</t>
   </si>
   <si>
@@ -121,49 +127,55 @@
     <t>ÁREA ADMINISTRATIVA</t>
   </si>
   <si>
-    <t>RF005 - Cadastro de bebidas</t>
+    <t>RF005 - Login de Administrador</t>
+  </si>
+  <si>
+    <t>O sistema deve permitir que somente administradores autenticados acessem a área administrativa utilizando email e senha.</t>
+  </si>
+  <si>
+    <t>RF006 - Cadastro de bebidas</t>
   </si>
   <si>
     <t>O sistema deve permitir o cadastro de bebidas.</t>
   </si>
   <si>
-    <t>RF006 - Consulta de bebidas</t>
+    <t>RF007 - Consulta de bebidas</t>
   </si>
   <si>
     <t>O sistema deve permitir a visualização das bebidas cadastradas.</t>
   </si>
   <si>
-    <t>RF007 - Edição de bebidas</t>
+    <t>RF008 - Edição de bebidas</t>
   </si>
   <si>
     <t>O sistema deve permitir a alteração dos dados de uma bebida.</t>
   </si>
   <si>
-    <t>RF008 - Exclusão de bebidas</t>
+    <t>RF009 - Exclusão de bebidas</t>
   </si>
   <si>
     <t>O sistema deve permitir a remoção de bebidas.</t>
   </si>
   <si>
-    <t>RF009 - Cadastro de categorias</t>
+    <t>RF010 - Cadastro de categorias</t>
   </si>
   <si>
     <t>O sistema deve permitir o cadastro de categorias.</t>
   </si>
   <si>
-    <t>RF010 - Consulta de categorias</t>
+    <t>RF011 - Consulta de categorias</t>
   </si>
   <si>
     <t>O sistema deve permitir a visualização das categorias cadastradas.</t>
   </si>
   <si>
-    <t>RF011 - Edição de categorias</t>
+    <t>RF012 - Edição de categorias</t>
   </si>
   <si>
     <t>O sistema deve permitir a alteração dos dados de uma categoria.</t>
   </si>
   <si>
-    <t>RF012 - Exclusão de categorias</t>
+    <t>RF013 - Exclusão de categorias</t>
   </si>
   <si>
     <t>O sistema deve permitir a remoção de categorias.</t>
@@ -172,19 +184,19 @@
     <t>API DA LANDING PAGE</t>
   </si>
   <si>
-    <t>RF013 - Listagem de bebidas</t>
+    <t>RF014 - Listagem de bebidas</t>
   </si>
   <si>
     <t>A API deve disponibilizar um endpoint para consulta das bebidas.</t>
   </si>
   <si>
-    <t>RF014 - Consulta de bebida por ID</t>
+    <t>RF015 - Consulta de bebida por ID</t>
   </si>
   <si>
     <t>A API deve disponibilizar um endpoint para consulta dos detalhes de uma bebida específica.</t>
   </si>
   <si>
-    <t>RF015 - Listagem de categorias</t>
+    <t>RF016 - Listagem de categorias</t>
   </si>
   <si>
     <t>A API deve disponibilizar um endpoint para consulta das categorias cadastradas.</t>
@@ -193,36 +205,42 @@
     <t>API ADMINISTRATIVA</t>
   </si>
   <si>
-    <t>RF016 - Cadastro via API</t>
+    <t>RF017 - Cadastro via API</t>
   </si>
   <si>
     <t>A API deve permitir o cadastro de bebidas e categorias.</t>
   </si>
   <si>
-    <t>RF017 - Atualização via API</t>
+    <t>RF018 - Atualização via API</t>
   </si>
   <si>
     <t>A API deve permitir a atualização de bebidas e categorias.</t>
   </si>
   <si>
-    <t>RF018 - Exclusão via API</t>
+    <t>RF019 - Exclusão via API</t>
   </si>
   <si>
     <t>A API deve permitir a exclusão de bebidas e categorias.</t>
   </si>
   <si>
-    <t>RF019 - Consulta via API</t>
+    <t>RF020 - Consulta via API</t>
   </si>
   <si>
     <t>A API deve permitir a consulta de todas as bebidas e de todas as categorias.</t>
   </si>
   <si>
-    <t>RF019 - Consulta por ID via API</t>
+    <t>RF021 - Consulta por ID via API</t>
   </si>
   <si>
     <t>A API deve permitir a consulta de uma bebida e de uma categoria pelo ID.</t>
   </si>
   <si>
+    <t>RF022 - Autenticação via API</t>
+  </si>
+  <si>
+    <t>A API deve disponibilizar um endpoint para login de administradores.</t>
+  </si>
+  <si>
     <t>Requisitos Não Funcionais</t>
   </si>
   <si>
@@ -337,9 +355,6 @@
     <t>Regra de Negócio</t>
   </si>
   <si>
-    <t>Exceções</t>
-  </si>
-  <si>
     <t>PRODUTOS</t>
   </si>
   <si>
@@ -355,7 +370,7 @@
     <t>RN002 - Obrigatoriedades dos Produtos</t>
   </si>
   <si>
-    <t>Não é permitido cadastrar uma bebida sem informar seu nome, sua categoria, sua marca, seu sabor sua embalagem e sua litragem.</t>
+    <t>Não é permitido cadastrar uma bebida sem informar nome, categoria, marca, sabor, embalagem, litragem, gaseificação e teor alcoólico.</t>
   </si>
   <si>
     <t>RN003 - Imagem do Produto</t>
@@ -376,25 +391,43 @@
     <t>Uma categoria não pode ser excluída enquanto possuir bebidas vinculadas, exceto se todas as bebidas vinculadas forem removidas ou transferidas para outra categoria.</t>
   </si>
   <si>
-    <t>RN005 - Gerenciamento de Produtos</t>
+    <t>RN005 - Autenticação</t>
   </si>
   <si>
     <t>Área Administrativa</t>
   </si>
   <si>
-    <t>Apenas a área administrativa pode cadastrar, editar ou excluir produtos.</t>
-  </si>
-  <si>
-    <t>RN006 - Gerenciamento de Categorias</t>
-  </si>
-  <si>
-    <t>Apenas a área administrativa pode cadastrar, editar ou excluir categorias.</t>
+    <t>O acesso à área administrativa somente será permitido mediante a autenticação de email e senha válidos.</t>
+  </si>
+  <si>
+    <t>RN006 - Obrigatoriedade dos Campos</t>
+  </si>
+  <si>
+    <t>O sistema não permitirá a realização do login caso os campos de email ou senha não sejam preenchidos.</t>
+  </si>
+  <si>
+    <t>RN007 - Não pode haver um cadastro de dois ou mais administradores com o mesmo email.</t>
+  </si>
+  <si>
+    <t>Não será permitido o cadastro de administradores com emails já existentes no sistema.</t>
+  </si>
+  <si>
+    <t>RN008 - Gerenciamento de Produtos</t>
+  </si>
+  <si>
+    <t>Apenas administradores autenticados poderão cadastrar, editar ou excluir produtos.</t>
+  </si>
+  <si>
+    <t>RN009 - Gerenciamento de Categorias</t>
+  </si>
+  <si>
+    <t>Apenas administradores autenticados poderão cadastrar, editar ou excluir categorias.</t>
   </si>
   <si>
     <t>CATÁLOGO</t>
   </si>
   <si>
-    <t>RN007 - Exibição de Produtos</t>
+    <t>RN010 - Exibição de Produtos</t>
   </si>
   <si>
     <t>Catálogo</t>
@@ -403,13 +436,13 @@
     <t>Somente produtos cadastrados no banco de dados podem ser exibidos na Landing Page.</t>
   </si>
   <si>
-    <t>RN008 - Organização por Categorias</t>
+    <t>RN011 - Organização por Categorias</t>
   </si>
   <si>
     <t>Os produtos devem ser exibidos agrupados de acordo com sua categoria cadastrada.</t>
   </si>
   <si>
-    <t>RN009 - Proibição de Vendas</t>
+    <t>RN012 - Proibição de Vendas</t>
   </si>
   <si>
     <t>Escopo do Projeto</t>
@@ -427,7 +460,7 @@
     <numFmt numFmtId="165" formatCode="d.m"/>
     <numFmt numFmtId="166" formatCode="dd/mm/yyyy"/>
   </numFmts>
-  <fonts count="10">
+  <fonts count="11">
     <font>
       <sz val="11.0"/>
       <color theme="1"/>
@@ -464,18 +497,23 @@
       <name val="Calibri"/>
     </font>
     <font>
+      <sz val="11.0"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
       <b/>
       <sz val="16.0"/>
       <color rgb="FFFFFFFF"/>
       <name val="Calibri"/>
     </font>
     <font>
+      <b/>
       <sz val="11.0"/>
-      <color rgb="FF000000"/>
+      <color rgb="FFFFFFFF"/>
       <name val="Calibri"/>
     </font>
     <font>
-      <b/>
       <sz val="11.0"/>
       <color rgb="FFFFFFFF"/>
       <name val="Calibri"/>
@@ -543,7 +581,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="15">
+  <borders count="13">
     <border/>
     <border>
       <left style="thin">
@@ -631,25 +669,11 @@
     <border>
       <left/>
       <right/>
-      <bottom/>
-    </border>
-    <border>
-      <left/>
-      <right/>
       <top/>
       <bottom/>
     </border>
     <border>
       <left/>
-      <top style="thin">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF000000"/>
-      </bottom>
-    </border>
-    <border>
-      <right/>
       <top style="thin">
         <color rgb="FF000000"/>
       </top>
@@ -669,7 +693,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="56">
+  <cellXfs count="53">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -699,28 +723,21 @@
     </xf>
     <xf borderId="8" fillId="0" fontId="2" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
     <xf borderId="9" fillId="0" fontId="2" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="5" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" vertical="center"/>
-    </xf>
-    <xf borderId="10" fillId="0" fontId="2" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
     <xf borderId="4" fillId="0" fontId="2" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
     <xf borderId="5" fillId="0" fontId="1" numFmtId="164" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf borderId="11" fillId="3" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="10" fillId="3" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf borderId="5" fillId="0" fontId="1" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
     <xf borderId="1" fillId="4" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf borderId="11" fillId="5" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf borderId="10" fillId="5" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf borderId="11" fillId="5" fontId="4" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="7" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" vertical="center"/>
-    </xf>
+    <xf borderId="10" fillId="5" fontId="4" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
     <xf borderId="7" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -728,20 +745,26 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf borderId="9" fillId="0" fontId="1" numFmtId="165" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf borderId="9" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
+    <xf borderId="9" fillId="0" fontId="1" numFmtId="166" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf borderId="9" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf borderId="9" fillId="0" fontId="1" numFmtId="165" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center" readingOrder="0" vertical="center"/>
     </xf>
     <xf borderId="9" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" readingOrder="0" vertical="center"/>
     </xf>
     <xf borderId="9" fillId="0" fontId="1" numFmtId="166" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center" readingOrder="0" vertical="center"/>
     </xf>
-    <xf borderId="9" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" vertical="center"/>
-    </xf>
-    <xf borderId="9" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf borderId="4" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -757,10 +780,9 @@
     <xf borderId="1" fillId="4" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf borderId="12" fillId="8" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf borderId="11" fillId="8" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf borderId="13" fillId="0" fontId="2" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
     <xf borderId="5" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
@@ -770,23 +792,23 @@
     <xf borderId="5" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="12" fillId="9" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf borderId="5" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
+    <xf borderId="1" fillId="0" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
+    <xf borderId="11" fillId="9" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf borderId="4" fillId="0" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="1" fillId="0" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="4" fillId="0" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
+    <xf borderId="1" fillId="0" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="left" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="14" fillId="0" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="12" fillId="0" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="4" fillId="0" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="1" fillId="0" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
     <xf borderId="1" fillId="10" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" vertical="center"/>
@@ -794,12 +816,6 @@
     <xf borderId="1" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf borderId="5" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="5" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
     <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
@@ -810,6 +826,9 @@
       <alignment shrinkToFit="0" wrapText="1"/>
     </xf>
     <xf borderId="1" fillId="10" fontId="9" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf borderId="5" fillId="4" fontId="10" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" vertical="center"/>
     </xf>
     <xf borderId="5" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
@@ -1040,7 +1059,7 @@
     <col customWidth="1" min="3" max="3" width="47.14"/>
     <col customWidth="1" min="4" max="4" width="40.29"/>
     <col customWidth="1" min="5" max="5" width="67.86"/>
-    <col customWidth="1" min="6" max="26" width="8.71"/>
+    <col customWidth="1" min="6" max="25" width="8.71"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1109,7 +1128,7 @@
       <c r="B5" s="10" t="s">
         <v>6</v>
       </c>
-      <c r="C5" s="13">
+      <c r="C5" s="7">
         <v>1.1952943382E10</v>
       </c>
       <c r="D5" s="11"/>
@@ -1120,31 +1139,31 @@
       <c r="B6" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="C6" s="13" t="s">
+      <c r="C6" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="D6" s="14"/>
-      <c r="E6" s="15"/>
+      <c r="D6" s="11"/>
+      <c r="E6" s="13"/>
     </row>
     <row r="7">
       <c r="A7" s="2"/>
       <c r="B7" s="10" t="s">
         <v>9</v>
       </c>
-      <c r="C7" s="16">
+      <c r="C7" s="14">
         <v>46176.0</v>
       </c>
-      <c r="D7" s="17" t="s">
+      <c r="D7" s="15" t="s">
         <v>10</v>
       </c>
-      <c r="E7" s="18"/>
+      <c r="E7" s="16"/>
     </row>
     <row r="8">
       <c r="A8" s="2"/>
     </row>
     <row r="9">
       <c r="A9" s="2"/>
-      <c r="B9" s="19" t="s">
+      <c r="B9" s="17" t="s">
         <v>11</v>
       </c>
       <c r="C9" s="4"/>
@@ -1153,62 +1172,70 @@
     </row>
     <row r="10">
       <c r="A10" s="2"/>
-      <c r="B10" s="20" t="s">
+      <c r="B10" s="18" t="s">
         <v>12</v>
       </c>
-      <c r="C10" s="21" t="s">
+      <c r="C10" s="19" t="s">
         <v>13</v>
       </c>
-      <c r="D10" s="21" t="s">
+      <c r="D10" s="19" t="s">
         <v>14</v>
       </c>
-      <c r="E10" s="21" t="s">
+      <c r="E10" s="19" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2"/>
-      <c r="B11" s="22" t="s">
+      <c r="B11" s="20" t="s">
         <v>16</v>
       </c>
-      <c r="C11" s="23" t="s">
+      <c r="C11" s="20" t="s">
         <v>17</v>
       </c>
-      <c r="D11" s="24">
+      <c r="D11" s="21">
         <v>46176.0</v>
       </c>
-      <c r="E11" s="23" t="s">
+      <c r="E11" s="20" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2"/>
-      <c r="B12" s="25">
+      <c r="B12" s="22">
         <v>46023.0</v>
       </c>
-      <c r="C12" s="26" t="s">
+      <c r="C12" s="23" t="s">
         <v>19</v>
       </c>
-      <c r="D12" s="27">
+      <c r="D12" s="24">
         <v>46178.0</v>
       </c>
-      <c r="E12" s="28" t="s">
+      <c r="E12" s="25" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2"/>
-      <c r="B13" s="29"/>
-      <c r="C13" s="29"/>
-      <c r="D13" s="29"/>
-      <c r="E13" s="29"/>
+      <c r="B13" s="26">
+        <v>46054.0</v>
+      </c>
+      <c r="C13" s="27" t="s">
+        <v>21</v>
+      </c>
+      <c r="D13" s="28">
+        <v>46179.0</v>
+      </c>
+      <c r="E13" s="27" t="s">
+        <v>22</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="2"/>
-      <c r="B14" s="29"/>
-      <c r="C14" s="29"/>
-      <c r="D14" s="29"/>
-      <c r="E14" s="29"/>
+      <c r="B14" s="25"/>
+      <c r="C14" s="25"/>
+      <c r="D14" s="25"/>
+      <c r="E14" s="25"/>
     </row>
     <row r="15">
       <c r="A15" s="2"/>
@@ -1219,90 +1246,125 @@
     </row>
     <row r="16">
       <c r="A16" s="2"/>
-      <c r="B16" s="29"/>
-      <c r="C16" s="29"/>
-      <c r="D16" s="29"/>
-      <c r="E16" s="29"/>
-    </row>
-    <row r="17">
+    </row>
+    <row r="17" ht="15.75" customHeight="1">
       <c r="A17" s="2"/>
-      <c r="B17" s="29"/>
-      <c r="C17" s="29"/>
-      <c r="D17" s="29"/>
-      <c r="E17" s="29"/>
-    </row>
-    <row r="18">
+    </row>
+    <row r="18" ht="15.75" customHeight="1">
       <c r="A18" s="2"/>
-      <c r="B18" s="29"/>
-      <c r="C18" s="29"/>
-      <c r="D18" s="29"/>
-      <c r="E18" s="29"/>
-    </row>
-    <row r="19">
+      <c r="B18" s="30" t="s">
+        <v>23</v>
+      </c>
+      <c r="C18" s="4"/>
+      <c r="D18" s="4"/>
+      <c r="E18" s="5"/>
+    </row>
+    <row r="19" ht="15.75" customHeight="1">
       <c r="A19" s="2"/>
-      <c r="B19" s="30"/>
-      <c r="C19" s="30"/>
-      <c r="D19" s="30"/>
-      <c r="E19" s="30"/>
-    </row>
-    <row r="20">
+      <c r="B19" s="31" t="s">
+        <v>24</v>
+      </c>
+      <c r="C19" s="4"/>
+      <c r="D19" s="4"/>
+      <c r="E19" s="5"/>
+    </row>
+    <row r="20" ht="15.75" customHeight="1">
       <c r="A20" s="2"/>
-    </row>
-    <row r="21" ht="15.75" customHeight="1">
+      <c r="B20" s="32" t="s">
+        <v>25</v>
+      </c>
+      <c r="C20" s="33" t="s">
+        <v>15</v>
+      </c>
+      <c r="D20" s="5"/>
+      <c r="E20" s="32" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="21" ht="24.75" customHeight="1">
       <c r="A21" s="2"/>
-    </row>
-    <row r="22" ht="15.75" customHeight="1">
+      <c r="B21" s="34" t="s">
+        <v>27</v>
+      </c>
+      <c r="C21" s="4"/>
+      <c r="D21" s="4"/>
+      <c r="E21" s="4"/>
+    </row>
+    <row r="22" ht="31.5" customHeight="1">
       <c r="A22" s="2"/>
-      <c r="B22" s="31" t="s">
-        <v>21</v>
-      </c>
-      <c r="C22" s="4"/>
-      <c r="D22" s="4"/>
-      <c r="E22" s="5"/>
-    </row>
-    <row r="23" ht="15.75" customHeight="1">
+      <c r="B22" s="35" t="s">
+        <v>28</v>
+      </c>
+      <c r="C22" s="36" t="s">
+        <v>29</v>
+      </c>
+      <c r="D22" s="5"/>
+      <c r="E22" s="37" t="s">
+        <v>30</v>
+      </c>
+      <c r="F22" s="1"/>
+      <c r="G22" s="1"/>
+      <c r="H22" s="1"/>
+      <c r="I22" s="1"/>
+      <c r="J22" s="1"/>
+      <c r="K22" s="1"/>
+      <c r="L22" s="1"/>
+      <c r="M22" s="1"/>
+      <c r="N22" s="1"/>
+      <c r="O22" s="1"/>
+      <c r="P22" s="1"/>
+      <c r="Q22" s="1"/>
+      <c r="R22" s="1"/>
+      <c r="S22" s="1"/>
+      <c r="T22" s="1"/>
+      <c r="U22" s="1"/>
+      <c r="V22" s="1"/>
+      <c r="W22" s="1"/>
+      <c r="X22" s="1"/>
+      <c r="Y22" s="1"/>
+      <c r="Z22" s="1"/>
+    </row>
+    <row r="23" ht="30.0" customHeight="1">
       <c r="A23" s="2"/>
-      <c r="B23" s="32" t="s">
-        <v>22</v>
-      </c>
-      <c r="C23" s="4"/>
-      <c r="D23" s="4"/>
-      <c r="E23" s="5"/>
-    </row>
-    <row r="24" ht="15.75" customHeight="1">
+      <c r="B23" s="35" t="s">
+        <v>31</v>
+      </c>
+      <c r="C23" s="36" t="s">
+        <v>32</v>
+      </c>
+      <c r="D23" s="5"/>
+      <c r="E23" s="37"/>
+    </row>
+    <row r="24" ht="24.75" customHeight="1">
       <c r="A24" s="2"/>
-      <c r="B24" s="33" t="s">
-        <v>23</v>
-      </c>
-      <c r="C24" s="34" t="s">
-        <v>15</v>
+      <c r="B24" s="35" t="s">
+        <v>33</v>
+      </c>
+      <c r="C24" s="36" t="s">
+        <v>34</v>
       </c>
       <c r="D24" s="5"/>
-      <c r="E24" s="33" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="25" ht="24.75" customHeight="1">
+      <c r="E24" s="37"/>
+    </row>
+    <row r="25" ht="33.0" customHeight="1">
       <c r="A25" s="2"/>
       <c r="B25" s="35" t="s">
-        <v>25</v>
-      </c>
-      <c r="C25" s="4"/>
-      <c r="D25" s="4"/>
-      <c r="E25" s="36"/>
-    </row>
-    <row r="26" ht="31.5" customHeight="1">
+        <v>35</v>
+      </c>
+      <c r="C25" s="36" t="s">
+        <v>36</v>
+      </c>
+      <c r="D25" s="5"/>
+      <c r="E25" s="37"/>
+    </row>
+    <row r="26" ht="24.75" customHeight="1">
       <c r="A26" s="2"/>
-      <c r="B26" s="37" t="s">
-        <v>26</v>
-      </c>
-      <c r="C26" s="38" t="s">
-        <v>27</v>
-      </c>
-      <c r="D26" s="5"/>
-      <c r="E26" s="39" t="s">
-        <v>28</v>
-      </c>
+      <c r="B26" s="34" t="s">
+        <v>37</v>
+      </c>
+      <c r="C26" s="4"/>
+      <c r="D26" s="4"/>
+      <c r="E26" s="4"/>
       <c r="F26" s="1"/>
       <c r="G26" s="1"/>
       <c r="H26" s="1"/>
@@ -1325,134 +1387,155 @@
       <c r="Y26" s="1"/>
       <c r="Z26" s="1"/>
     </row>
-    <row r="27" ht="30.0" customHeight="1">
+    <row r="27" ht="31.5" customHeight="1">
       <c r="A27" s="2"/>
-      <c r="B27" s="37" t="s">
-        <v>29</v>
-      </c>
-      <c r="C27" s="38" t="s">
-        <v>30</v>
+      <c r="B27" s="38" t="s">
+        <v>38</v>
+      </c>
+      <c r="C27" s="39" t="s">
+        <v>39</v>
       </c>
       <c r="D27" s="5"/>
-      <c r="E27" s="39"/>
-    </row>
-    <row r="28" ht="24.75" customHeight="1">
+      <c r="E27" s="37"/>
+    </row>
+    <row r="28" ht="22.5" customHeight="1">
       <c r="A28" s="2"/>
-      <c r="B28" s="37" t="s">
-        <v>31</v>
-      </c>
-      <c r="C28" s="38" t="s">
-        <v>32</v>
+      <c r="B28" s="38" t="s">
+        <v>40</v>
+      </c>
+      <c r="C28" s="36" t="s">
+        <v>41</v>
       </c>
       <c r="D28" s="5"/>
-      <c r="E28" s="39"/>
-    </row>
-    <row r="29" ht="33.0" customHeight="1">
+      <c r="E28" s="37"/>
+    </row>
+    <row r="29" ht="22.5" customHeight="1">
       <c r="A29" s="2"/>
-      <c r="B29" s="37" t="s">
-        <v>33</v>
-      </c>
-      <c r="C29" s="38" t="s">
-        <v>34</v>
+      <c r="B29" s="38" t="s">
+        <v>42</v>
+      </c>
+      <c r="C29" s="36" t="s">
+        <v>43</v>
       </c>
       <c r="D29" s="5"/>
-      <c r="E29" s="39"/>
-    </row>
-    <row r="30" ht="24.75" customHeight="1">
+      <c r="E29" s="37"/>
+    </row>
+    <row r="30" ht="22.5" customHeight="1">
       <c r="A30" s="2"/>
-      <c r="B30" s="35" t="s">
-        <v>35</v>
-      </c>
-      <c r="C30" s="4"/>
-      <c r="D30" s="4"/>
-      <c r="E30" s="36"/>
-      <c r="F30" s="1"/>
-      <c r="G30" s="1"/>
-      <c r="H30" s="1"/>
-      <c r="I30" s="1"/>
-      <c r="J30" s="1"/>
-      <c r="K30" s="1"/>
-      <c r="L30" s="1"/>
-      <c r="M30" s="1"/>
-      <c r="N30" s="1"/>
-      <c r="O30" s="1"/>
-      <c r="P30" s="1"/>
-      <c r="Q30" s="1"/>
-      <c r="R30" s="1"/>
-      <c r="S30" s="1"/>
-      <c r="T30" s="1"/>
-      <c r="U30" s="1"/>
-      <c r="V30" s="1"/>
-      <c r="W30" s="1"/>
-      <c r="X30" s="1"/>
-      <c r="Y30" s="1"/>
-      <c r="Z30" s="1"/>
+      <c r="B30" s="38" t="s">
+        <v>44</v>
+      </c>
+      <c r="C30" s="36" t="s">
+        <v>45</v>
+      </c>
+      <c r="D30" s="5"/>
+      <c r="E30" s="37"/>
     </row>
     <row r="31" ht="22.5" customHeight="1">
       <c r="A31" s="2"/>
-      <c r="B31" s="37" t="s">
-        <v>36</v>
-      </c>
-      <c r="C31" s="38" t="s">
-        <v>37</v>
+      <c r="B31" s="38" t="s">
+        <v>46</v>
+      </c>
+      <c r="C31" s="36" t="s">
+        <v>47</v>
       </c>
       <c r="D31" s="5"/>
-      <c r="E31" s="39"/>
+      <c r="E31" s="37"/>
     </row>
     <row r="32" ht="22.5" customHeight="1">
       <c r="A32" s="2"/>
-      <c r="B32" s="37" t="s">
-        <v>38</v>
-      </c>
-      <c r="C32" s="38" t="s">
-        <v>39</v>
+      <c r="B32" s="38" t="s">
+        <v>48</v>
+      </c>
+      <c r="C32" s="36" t="s">
+        <v>49</v>
       </c>
       <c r="D32" s="5"/>
-      <c r="E32" s="39"/>
+      <c r="E32" s="37"/>
     </row>
     <row r="33" ht="22.5" customHeight="1">
       <c r="A33" s="2"/>
-      <c r="B33" s="37" t="s">
-        <v>40</v>
-      </c>
-      <c r="C33" s="38" t="s">
-        <v>41</v>
+      <c r="B33" s="38" t="s">
+        <v>50</v>
+      </c>
+      <c r="C33" s="36" t="s">
+        <v>51</v>
       </c>
       <c r="D33" s="5"/>
-      <c r="E33" s="39"/>
+      <c r="E33" s="37"/>
+      <c r="F33" s="1"/>
+      <c r="G33" s="1"/>
+      <c r="H33" s="1"/>
+      <c r="I33" s="1"/>
+      <c r="J33" s="1"/>
+      <c r="K33" s="1"/>
+      <c r="L33" s="1"/>
+      <c r="M33" s="1"/>
+      <c r="N33" s="1"/>
+      <c r="O33" s="1"/>
+      <c r="P33" s="1"/>
+      <c r="Q33" s="1"/>
+      <c r="R33" s="1"/>
+      <c r="S33" s="1"/>
+      <c r="T33" s="1"/>
+      <c r="U33" s="1"/>
+      <c r="V33" s="1"/>
+      <c r="W33" s="1"/>
+      <c r="X33" s="1"/>
+      <c r="Y33" s="1"/>
+      <c r="Z33" s="1"/>
     </row>
     <row r="34" ht="22.5" customHeight="1">
       <c r="A34" s="2"/>
-      <c r="B34" s="37" t="s">
-        <v>42</v>
-      </c>
-      <c r="C34" s="38" t="s">
-        <v>43</v>
+      <c r="B34" s="38" t="s">
+        <v>52</v>
+      </c>
+      <c r="C34" s="36" t="s">
+        <v>53</v>
       </c>
       <c r="D34" s="5"/>
-      <c r="E34" s="39"/>
-    </row>
-    <row r="35" ht="22.5" customHeight="1">
+      <c r="E34" s="37"/>
+    </row>
+    <row r="35" ht="26.25" customHeight="1">
       <c r="A35" s="2"/>
-      <c r="B35" s="37" t="s">
-        <v>44</v>
-      </c>
-      <c r="C35" s="38" t="s">
-        <v>45</v>
+      <c r="B35" s="38" t="s">
+        <v>54</v>
+      </c>
+      <c r="C35" s="36" t="s">
+        <v>55</v>
       </c>
       <c r="D35" s="5"/>
-      <c r="E35" s="39"/>
-    </row>
-    <row r="36" ht="22.5" customHeight="1">
+      <c r="E35" s="37"/>
+      <c r="F35" s="1"/>
+      <c r="G35" s="1"/>
+      <c r="H35" s="1"/>
+      <c r="I35" s="1"/>
+      <c r="J35" s="1"/>
+      <c r="K35" s="1"/>
+      <c r="L35" s="1"/>
+      <c r="M35" s="1"/>
+      <c r="N35" s="1"/>
+      <c r="O35" s="1"/>
+      <c r="P35" s="1"/>
+      <c r="Q35" s="1"/>
+      <c r="R35" s="1"/>
+      <c r="S35" s="1"/>
+      <c r="T35" s="1"/>
+      <c r="U35" s="1"/>
+      <c r="V35" s="1"/>
+      <c r="W35" s="1"/>
+      <c r="X35" s="1"/>
+      <c r="Y35" s="1"/>
+      <c r="Z35" s="1"/>
+    </row>
+    <row r="36" ht="24.75" customHeight="1">
       <c r="A36" s="2"/>
-      <c r="B36" s="37" t="s">
-        <v>46</v>
-      </c>
-      <c r="C36" s="38" t="s">
-        <v>47</v>
-      </c>
-      <c r="D36" s="5"/>
-      <c r="E36" s="39"/>
+      <c r="B36" s="40" t="s">
+        <v>56</v>
+      </c>
+      <c r="C36" s="4"/>
+      <c r="D36" s="4"/>
+      <c r="E36" s="4"/>
       <c r="F36" s="1"/>
       <c r="G36" s="1"/>
       <c r="H36" s="1"/>
@@ -1475,27 +1558,48 @@
       <c r="Y36" s="1"/>
       <c r="Z36" s="1"/>
     </row>
-    <row r="37" ht="22.5" customHeight="1">
+    <row r="37" ht="31.5" customHeight="1">
       <c r="A37" s="2"/>
-      <c r="B37" s="37" t="s">
-        <v>48</v>
-      </c>
-      <c r="C37" s="38" t="s">
-        <v>49</v>
+      <c r="B37" s="41" t="s">
+        <v>57</v>
+      </c>
+      <c r="C37" s="42" t="s">
+        <v>58</v>
       </c>
       <c r="D37" s="5"/>
-      <c r="E37" s="39"/>
-    </row>
-    <row r="38" ht="26.25" customHeight="1">
+      <c r="E37" s="43"/>
+      <c r="F37" s="1"/>
+      <c r="G37" s="1"/>
+      <c r="H37" s="1"/>
+      <c r="I37" s="1"/>
+      <c r="J37" s="1"/>
+      <c r="K37" s="1"/>
+      <c r="L37" s="1"/>
+      <c r="M37" s="1"/>
+      <c r="N37" s="1"/>
+      <c r="O37" s="1"/>
+      <c r="P37" s="1"/>
+      <c r="Q37" s="1"/>
+      <c r="R37" s="1"/>
+      <c r="S37" s="1"/>
+      <c r="T37" s="1"/>
+      <c r="U37" s="1"/>
+      <c r="V37" s="1"/>
+      <c r="W37" s="1"/>
+      <c r="X37" s="1"/>
+      <c r="Y37" s="1"/>
+      <c r="Z37" s="1"/>
+    </row>
+    <row r="38" ht="31.5" customHeight="1">
       <c r="A38" s="2"/>
-      <c r="B38" s="37" t="s">
-        <v>50</v>
-      </c>
-      <c r="C38" s="38" t="s">
-        <v>51</v>
+      <c r="B38" s="41" t="s">
+        <v>59</v>
+      </c>
+      <c r="C38" s="42" t="s">
+        <v>60</v>
       </c>
       <c r="D38" s="5"/>
-      <c r="E38" s="39"/>
+      <c r="E38" s="43"/>
       <c r="F38" s="1"/>
       <c r="G38" s="1"/>
       <c r="H38" s="1"/>
@@ -1518,14 +1622,16 @@
       <c r="Y38" s="1"/>
       <c r="Z38" s="1"/>
     </row>
-    <row r="39" ht="24.75" customHeight="1">
+    <row r="39" ht="31.5" customHeight="1">
       <c r="A39" s="2"/>
-      <c r="B39" s="40" t="s">
-        <v>52</v>
-      </c>
-      <c r="C39" s="4"/>
-      <c r="D39" s="4"/>
-      <c r="E39" s="36"/>
+      <c r="B39" s="41" t="s">
+        <v>61</v>
+      </c>
+      <c r="C39" s="42" t="s">
+        <v>62</v>
+      </c>
+      <c r="D39" s="5"/>
+      <c r="E39" s="43"/>
       <c r="F39" s="1"/>
       <c r="G39" s="1"/>
       <c r="H39" s="1"/>
@@ -1548,16 +1654,14 @@
       <c r="Y39" s="1"/>
       <c r="Z39" s="1"/>
     </row>
-    <row r="40" ht="31.5" customHeight="1">
+    <row r="40" ht="24.75" customHeight="1">
       <c r="A40" s="2"/>
-      <c r="B40" s="41" t="s">
-        <v>53</v>
-      </c>
-      <c r="C40" s="42" t="s">
-        <v>54</v>
-      </c>
-      <c r="D40" s="5"/>
-      <c r="E40" s="43"/>
+      <c r="B40" s="40" t="s">
+        <v>63</v>
+      </c>
+      <c r="C40" s="4"/>
+      <c r="D40" s="4"/>
+      <c r="E40" s="4"/>
       <c r="F40" s="1"/>
       <c r="G40" s="1"/>
       <c r="H40" s="1"/>
@@ -1583,10 +1687,10 @@
     <row r="41" ht="31.5" customHeight="1">
       <c r="A41" s="2"/>
       <c r="B41" s="41" t="s">
-        <v>55</v>
+        <v>64</v>
       </c>
       <c r="C41" s="42" t="s">
-        <v>56</v>
+        <v>65</v>
       </c>
       <c r="D41" s="5"/>
       <c r="E41" s="43"/>
@@ -1615,10 +1719,10 @@
     <row r="42" ht="31.5" customHeight="1">
       <c r="A42" s="2"/>
       <c r="B42" s="41" t="s">
-        <v>57</v>
+        <v>66</v>
       </c>
       <c r="C42" s="42" t="s">
-        <v>58</v>
+        <v>67</v>
       </c>
       <c r="D42" s="5"/>
       <c r="E42" s="43"/>
@@ -1644,14 +1748,16 @@
       <c r="Y42" s="1"/>
       <c r="Z42" s="1"/>
     </row>
-    <row r="43" ht="24.75" customHeight="1">
+    <row r="43" ht="31.5" customHeight="1">
       <c r="A43" s="2"/>
-      <c r="B43" s="40" t="s">
-        <v>59</v>
-      </c>
-      <c r="C43" s="4"/>
-      <c r="D43" s="4"/>
-      <c r="E43" s="36"/>
+      <c r="B43" s="41" t="s">
+        <v>68</v>
+      </c>
+      <c r="C43" s="42" t="s">
+        <v>69</v>
+      </c>
+      <c r="D43" s="5"/>
+      <c r="E43" s="43"/>
       <c r="F43" s="1"/>
       <c r="G43" s="1"/>
       <c r="H43" s="1"/>
@@ -1674,13 +1780,13 @@
       <c r="Y43" s="1"/>
       <c r="Z43" s="1"/>
     </row>
-    <row r="44" ht="31.5" customHeight="1">
+    <row r="44" ht="32.25" customHeight="1">
       <c r="A44" s="2"/>
       <c r="B44" s="41" t="s">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="C44" s="42" t="s">
-        <v>61</v>
+        <v>71</v>
       </c>
       <c r="D44" s="5"/>
       <c r="E44" s="43"/>
@@ -1706,13 +1812,13 @@
       <c r="Y44" s="1"/>
       <c r="Z44" s="1"/>
     </row>
-    <row r="45" ht="31.5" customHeight="1">
+    <row r="45" ht="32.25" customHeight="1">
       <c r="A45" s="2"/>
       <c r="B45" s="41" t="s">
-        <v>62</v>
+        <v>72</v>
       </c>
       <c r="C45" s="42" t="s">
-        <v>63</v>
+        <v>73</v>
       </c>
       <c r="D45" s="5"/>
       <c r="E45" s="43"/>
@@ -1738,269 +1844,248 @@
       <c r="Y45" s="1"/>
       <c r="Z45" s="1"/>
     </row>
-    <row r="46" ht="31.5" customHeight="1">
+    <row r="46" ht="23.25" customHeight="1">
       <c r="A46" s="2"/>
       <c r="B46" s="41" t="s">
-        <v>64</v>
-      </c>
-      <c r="C46" s="42" t="s">
-        <v>65</v>
+        <v>74</v>
+      </c>
+      <c r="C46" s="39" t="s">
+        <v>75</v>
       </c>
       <c r="D46" s="5"/>
       <c r="E46" s="43"/>
-      <c r="F46" s="1"/>
-      <c r="G46" s="1"/>
-      <c r="H46" s="1"/>
-      <c r="I46" s="1"/>
-      <c r="J46" s="1"/>
-      <c r="K46" s="1"/>
-      <c r="L46" s="1"/>
-      <c r="M46" s="1"/>
-      <c r="N46" s="1"/>
-      <c r="O46" s="1"/>
-      <c r="P46" s="1"/>
-      <c r="Q46" s="1"/>
-      <c r="R46" s="1"/>
-      <c r="S46" s="1"/>
-      <c r="T46" s="1"/>
-      <c r="U46" s="1"/>
-      <c r="V46" s="1"/>
-      <c r="W46" s="1"/>
-      <c r="X46" s="1"/>
-      <c r="Y46" s="1"/>
-      <c r="Z46" s="1"/>
-    </row>
-    <row r="47" ht="32.25" customHeight="1">
+    </row>
+    <row r="47" ht="15.0" customHeight="1">
       <c r="A47" s="2"/>
-      <c r="B47" s="44" t="s">
-        <v>66</v>
-      </c>
-      <c r="C47" s="45" t="s">
-        <v>67</v>
-      </c>
-      <c r="D47" s="5"/>
-      <c r="E47" s="43"/>
-      <c r="F47" s="1"/>
-      <c r="G47" s="1"/>
-      <c r="H47" s="1"/>
-      <c r="I47" s="1"/>
-      <c r="J47" s="1"/>
-      <c r="K47" s="1"/>
-      <c r="L47" s="1"/>
-      <c r="M47" s="1"/>
-      <c r="N47" s="1"/>
-      <c r="O47" s="1"/>
-      <c r="P47" s="1"/>
-      <c r="Q47" s="1"/>
-      <c r="R47" s="1"/>
-      <c r="S47" s="1"/>
-      <c r="T47" s="1"/>
-      <c r="U47" s="1"/>
-      <c r="V47" s="1"/>
-      <c r="W47" s="1"/>
-      <c r="X47" s="1"/>
-      <c r="Y47" s="1"/>
-      <c r="Z47" s="1"/>
-    </row>
-    <row r="48" ht="32.25" customHeight="1">
+      <c r="B47" s="1"/>
+      <c r="C47" s="1"/>
+      <c r="D47" s="1"/>
+      <c r="E47" s="1"/>
+    </row>
+    <row r="48" ht="15.0" customHeight="1">
       <c r="A48" s="2"/>
       <c r="B48" s="44" t="s">
-        <v>68</v>
-      </c>
-      <c r="C48" s="45" t="s">
-        <v>69</v>
-      </c>
-      <c r="D48" s="5"/>
-      <c r="E48" s="43"/>
-      <c r="F48" s="1"/>
-      <c r="G48" s="1"/>
-      <c r="H48" s="1"/>
-      <c r="I48" s="1"/>
-      <c r="J48" s="1"/>
-      <c r="K48" s="1"/>
-      <c r="L48" s="1"/>
-      <c r="M48" s="1"/>
-      <c r="N48" s="1"/>
-      <c r="O48" s="1"/>
-      <c r="P48" s="1"/>
-      <c r="Q48" s="1"/>
-      <c r="R48" s="1"/>
-      <c r="S48" s="1"/>
-      <c r="T48" s="1"/>
-      <c r="U48" s="1"/>
-      <c r="V48" s="1"/>
-      <c r="W48" s="1"/>
-      <c r="X48" s="1"/>
-      <c r="Y48" s="1"/>
-      <c r="Z48" s="1"/>
+        <v>76</v>
+      </c>
+      <c r="C48" s="4"/>
+      <c r="D48" s="4"/>
+      <c r="E48" s="5"/>
     </row>
     <row r="49" ht="15.0" customHeight="1">
       <c r="A49" s="2"/>
-      <c r="B49" s="1"/>
-      <c r="C49" s="1"/>
-      <c r="D49" s="1"/>
-      <c r="E49" s="1"/>
-    </row>
-    <row r="50" ht="15.0" customHeight="1">
+      <c r="B49" s="32" t="s">
+        <v>25</v>
+      </c>
+      <c r="C49" s="33" t="s">
+        <v>77</v>
+      </c>
+      <c r="D49" s="5"/>
+      <c r="E49" s="32" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="50" ht="24.75" customHeight="1">
       <c r="A50" s="2"/>
-      <c r="B50" s="46" t="s">
-        <v>70</v>
+      <c r="B50" s="40" t="s">
+        <v>27</v>
       </c>
       <c r="C50" s="4"/>
       <c r="D50" s="4"/>
-      <c r="E50" s="5"/>
-    </row>
-    <row r="51" ht="15.0" customHeight="1">
+      <c r="E50" s="4"/>
+    </row>
+    <row r="51" ht="31.5" customHeight="1">
       <c r="A51" s="2"/>
-      <c r="B51" s="33" t="s">
-        <v>23</v>
-      </c>
-      <c r="C51" s="34" t="s">
-        <v>71</v>
+      <c r="B51" s="37" t="s">
+        <v>78</v>
+      </c>
+      <c r="C51" s="45" t="s">
+        <v>79</v>
       </c>
       <c r="D51" s="5"/>
-      <c r="E51" s="33" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="52" ht="24.75" customHeight="1">
+      <c r="E51" s="37" t="s">
+        <v>80</v>
+      </c>
+      <c r="F51" s="1"/>
+      <c r="G51" s="1"/>
+      <c r="H51" s="1"/>
+      <c r="I51" s="1"/>
+      <c r="J51" s="1"/>
+      <c r="K51" s="1"/>
+      <c r="L51" s="1"/>
+      <c r="M51" s="1"/>
+      <c r="N51" s="1"/>
+      <c r="O51" s="1"/>
+      <c r="P51" s="1"/>
+      <c r="Q51" s="1"/>
+      <c r="R51" s="1"/>
+      <c r="S51" s="1"/>
+      <c r="T51" s="1"/>
+      <c r="U51" s="1"/>
+      <c r="V51" s="1"/>
+      <c r="W51" s="1"/>
+      <c r="X51" s="1"/>
+      <c r="Y51" s="1"/>
+      <c r="Z51" s="1"/>
+    </row>
+    <row r="52" ht="33.0" customHeight="1">
       <c r="A52" s="2"/>
-      <c r="B52" s="40" t="s">
-        <v>25</v>
-      </c>
-      <c r="C52" s="4"/>
-      <c r="D52" s="4"/>
-      <c r="E52" s="36"/>
-    </row>
-    <row r="53" ht="31.5" customHeight="1">
+      <c r="B52" s="7" t="s">
+        <v>81</v>
+      </c>
+      <c r="C52" s="45" t="s">
+        <v>79</v>
+      </c>
+      <c r="D52" s="5"/>
+      <c r="E52" s="37" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="53" ht="33.75" customHeight="1">
       <c r="A53" s="2"/>
-      <c r="B53" s="39" t="s">
-        <v>72</v>
-      </c>
-      <c r="C53" s="47" t="s">
-        <v>73</v>
+      <c r="B53" s="37" t="s">
+        <v>83</v>
+      </c>
+      <c r="C53" s="45" t="s">
+        <v>84</v>
       </c>
       <c r="D53" s="5"/>
-      <c r="E53" s="39" t="s">
-        <v>74</v>
-      </c>
-      <c r="F53" s="1"/>
-      <c r="G53" s="1"/>
-      <c r="H53" s="1"/>
-      <c r="I53" s="1"/>
-      <c r="J53" s="1"/>
-      <c r="K53" s="1"/>
-      <c r="L53" s="1"/>
-      <c r="M53" s="1"/>
-      <c r="N53" s="1"/>
-      <c r="O53" s="1"/>
-      <c r="P53" s="1"/>
-      <c r="Q53" s="1"/>
-      <c r="R53" s="1"/>
-      <c r="S53" s="1"/>
-      <c r="T53" s="1"/>
-      <c r="U53" s="1"/>
-      <c r="V53" s="1"/>
-      <c r="W53" s="1"/>
-      <c r="X53" s="1"/>
-      <c r="Y53" s="1"/>
-      <c r="Z53" s="1"/>
-    </row>
-    <row r="54" ht="33.0" customHeight="1">
+      <c r="E53" s="37" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="54" ht="24.75" customHeight="1">
       <c r="A54" s="2"/>
-      <c r="B54" s="7" t="s">
-        <v>75</v>
-      </c>
-      <c r="C54" s="47" t="s">
-        <v>73</v>
-      </c>
-      <c r="D54" s="5"/>
-      <c r="E54" s="39" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="55" ht="33.75" customHeight="1">
+      <c r="B54" s="40" t="s">
+        <v>37</v>
+      </c>
+      <c r="C54" s="4"/>
+      <c r="D54" s="4"/>
+      <c r="E54" s="4"/>
+    </row>
+    <row r="55" ht="35.25" customHeight="1">
       <c r="A55" s="2"/>
-      <c r="B55" s="39" t="s">
-        <v>77</v>
-      </c>
-      <c r="C55" s="47" t="s">
-        <v>78</v>
+      <c r="B55" s="37" t="s">
+        <v>86</v>
+      </c>
+      <c r="C55" s="45" t="s">
+        <v>79</v>
       </c>
       <c r="D55" s="5"/>
-      <c r="E55" s="48" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="56" ht="24.75" customHeight="1">
+      <c r="E55" s="37" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="56" ht="30.75" customHeight="1">
       <c r="A56" s="2"/>
-      <c r="B56" s="40" t="s">
-        <v>35</v>
-      </c>
-      <c r="C56" s="4"/>
-      <c r="D56" s="4"/>
-      <c r="E56" s="36"/>
-    </row>
-    <row r="57" ht="35.25" customHeight="1">
+      <c r="B56" s="37" t="s">
+        <v>88</v>
+      </c>
+      <c r="C56" s="45" t="s">
+        <v>89</v>
+      </c>
+      <c r="D56" s="5"/>
+      <c r="E56" s="37" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="57" ht="15.75" customHeight="1">
       <c r="A57" s="2"/>
-      <c r="B57" s="39" t="s">
-        <v>80</v>
-      </c>
-      <c r="C57" s="47" t="s">
-        <v>73</v>
+      <c r="B57" s="37" t="s">
+        <v>91</v>
+      </c>
+      <c r="C57" s="45" t="s">
+        <v>84</v>
       </c>
       <c r="D57" s="5"/>
-      <c r="E57" s="39" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="58" ht="30.75" customHeight="1">
+      <c r="E57" s="37" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="58" ht="24.75" customHeight="1">
       <c r="A58" s="2"/>
-      <c r="B58" s="39" t="s">
-        <v>82</v>
-      </c>
-      <c r="C58" s="47" t="s">
-        <v>83</v>
-      </c>
-      <c r="D58" s="5"/>
-      <c r="E58" s="48" t="s">
+      <c r="B58" s="40" t="s">
+        <v>93</v>
+      </c>
+      <c r="C58" s="4"/>
+      <c r="D58" s="4"/>
+      <c r="E58" s="4"/>
+    </row>
+    <row r="59" ht="31.5" customHeight="1">
+      <c r="A59" s="2"/>
+      <c r="B59" s="37" t="s">
+        <v>94</v>
+      </c>
+      <c r="C59" s="45" t="s">
+        <v>95</v>
+      </c>
+      <c r="D59" s="5"/>
+      <c r="E59" s="35" t="s">
+        <v>96</v>
+      </c>
+      <c r="F59" s="1"/>
+      <c r="G59" s="1"/>
+      <c r="H59" s="1"/>
+      <c r="I59" s="1"/>
+      <c r="J59" s="1"/>
+      <c r="K59" s="1"/>
+      <c r="L59" s="1"/>
+      <c r="M59" s="1"/>
+      <c r="N59" s="1"/>
+      <c r="O59" s="1"/>
+      <c r="P59" s="1"/>
+      <c r="Q59" s="1"/>
+      <c r="R59" s="1"/>
+      <c r="S59" s="1"/>
+      <c r="T59" s="1"/>
+      <c r="U59" s="1"/>
+      <c r="V59" s="1"/>
+      <c r="W59" s="1"/>
+      <c r="X59" s="1"/>
+      <c r="Y59" s="1"/>
+      <c r="Z59" s="1"/>
+    </row>
+    <row r="60" ht="33.75" customHeight="1">
+      <c r="A60" s="2"/>
+      <c r="B60" s="37" t="s">
+        <v>97</v>
+      </c>
+      <c r="C60" s="45" t="s">
         <v>84</v>
       </c>
-    </row>
-    <row r="59" ht="15.75" customHeight="1">
-      <c r="A59" s="2"/>
-      <c r="B59" s="39" t="s">
-        <v>85</v>
-      </c>
-      <c r="C59" s="47" t="s">
-        <v>78</v>
-      </c>
-      <c r="D59" s="5"/>
-      <c r="E59" s="48" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="60" ht="24.75" customHeight="1">
-      <c r="A60" s="2"/>
-      <c r="B60" s="40" t="s">
-        <v>87</v>
-      </c>
-      <c r="C60" s="4"/>
-      <c r="D60" s="4"/>
-      <c r="E60" s="36"/>
-    </row>
-    <row r="61" ht="31.5" customHeight="1">
+      <c r="D60" s="5"/>
+      <c r="E60" s="35" t="s">
+        <v>98</v>
+      </c>
+      <c r="F60" s="1"/>
+      <c r="G60" s="1"/>
+      <c r="H60" s="1"/>
+      <c r="I60" s="1"/>
+      <c r="J60" s="1"/>
+      <c r="K60" s="1"/>
+      <c r="L60" s="1"/>
+      <c r="M60" s="1"/>
+      <c r="N60" s="1"/>
+      <c r="O60" s="1"/>
+      <c r="P60" s="1"/>
+      <c r="Q60" s="1"/>
+      <c r="R60" s="1"/>
+      <c r="S60" s="1"/>
+      <c r="T60" s="1"/>
+      <c r="U60" s="1"/>
+      <c r="V60" s="1"/>
+      <c r="W60" s="1"/>
+      <c r="X60" s="1"/>
+      <c r="Y60" s="1"/>
+      <c r="Z60" s="1"/>
+    </row>
+    <row r="61" ht="24.75" customHeight="1">
       <c r="A61" s="2"/>
-      <c r="B61" s="39" t="s">
-        <v>88</v>
-      </c>
-      <c r="C61" s="47" t="s">
-        <v>89</v>
-      </c>
-      <c r="D61" s="5"/>
-      <c r="E61" s="37" t="s">
-        <v>90</v>
-      </c>
+      <c r="B61" s="40" t="s">
+        <v>99</v>
+      </c>
+      <c r="C61" s="4"/>
+      <c r="D61" s="4"/>
+      <c r="E61" s="4"/>
       <c r="F61" s="1"/>
       <c r="G61" s="1"/>
       <c r="H61" s="1"/>
@@ -2023,17 +2108,17 @@
       <c r="Y61" s="1"/>
       <c r="Z61" s="1"/>
     </row>
-    <row r="62" ht="33.75" customHeight="1">
+    <row r="62" ht="19.5" customHeight="1">
       <c r="A62" s="2"/>
-      <c r="B62" s="39" t="s">
-        <v>91</v>
-      </c>
-      <c r="C62" s="47" t="s">
-        <v>78</v>
+      <c r="B62" s="37" t="s">
+        <v>100</v>
+      </c>
+      <c r="C62" s="45" t="s">
+        <v>89</v>
       </c>
       <c r="D62" s="5"/>
-      <c r="E62" s="37" t="s">
-        <v>92</v>
+      <c r="E62" s="35" t="s">
+        <v>101</v>
       </c>
       <c r="F62" s="1"/>
       <c r="G62" s="1"/>
@@ -2057,14 +2142,18 @@
       <c r="Y62" s="1"/>
       <c r="Z62" s="1"/>
     </row>
-    <row r="63" ht="24.75" customHeight="1">
+    <row r="63" ht="31.5" customHeight="1">
       <c r="A63" s="2"/>
-      <c r="B63" s="40" t="s">
-        <v>93</v>
-      </c>
-      <c r="C63" s="4"/>
-      <c r="D63" s="4"/>
-      <c r="E63" s="36"/>
+      <c r="B63" s="37" t="s">
+        <v>102</v>
+      </c>
+      <c r="C63" s="45" t="s">
+        <v>89</v>
+      </c>
+      <c r="D63" s="5"/>
+      <c r="E63" s="35" t="s">
+        <v>103</v>
+      </c>
       <c r="F63" s="1"/>
       <c r="G63" s="1"/>
       <c r="H63" s="1"/>
@@ -2087,18 +2176,14 @@
       <c r="Y63" s="1"/>
       <c r="Z63" s="1"/>
     </row>
-    <row r="64" ht="19.5" customHeight="1">
+    <row r="64" ht="24.75" customHeight="1">
       <c r="A64" s="2"/>
-      <c r="B64" s="39" t="s">
-        <v>94</v>
-      </c>
-      <c r="C64" s="47" t="s">
-        <v>83</v>
-      </c>
-      <c r="D64" s="5"/>
-      <c r="E64" s="37" t="s">
-        <v>95</v>
-      </c>
+      <c r="B64" s="40" t="s">
+        <v>104</v>
+      </c>
+      <c r="C64" s="4"/>
+      <c r="D64" s="4"/>
+      <c r="E64" s="4"/>
       <c r="F64" s="1"/>
       <c r="G64" s="1"/>
       <c r="H64" s="1"/>
@@ -2121,17 +2206,17 @@
       <c r="Y64" s="1"/>
       <c r="Z64" s="1"/>
     </row>
-    <row r="65" ht="31.5" customHeight="1">
+    <row r="65" ht="15.75" customHeight="1">
       <c r="A65" s="2"/>
-      <c r="B65" s="39" t="s">
-        <v>96</v>
-      </c>
-      <c r="C65" s="47" t="s">
-        <v>83</v>
+      <c r="B65" s="37" t="s">
+        <v>105</v>
+      </c>
+      <c r="C65" s="45" t="s">
+        <v>106</v>
       </c>
       <c r="D65" s="5"/>
-      <c r="E65" s="49" t="s">
-        <v>97</v>
+      <c r="E65" s="35" t="s">
+        <v>107</v>
       </c>
       <c r="F65" s="1"/>
       <c r="G65" s="1"/>
@@ -2155,14 +2240,18 @@
       <c r="Y65" s="1"/>
       <c r="Z65" s="1"/>
     </row>
-    <row r="66" ht="24.75" customHeight="1">
+    <row r="66" ht="15.75" customHeight="1">
       <c r="A66" s="2"/>
-      <c r="B66" s="40" t="s">
-        <v>98</v>
-      </c>
-      <c r="C66" s="4"/>
-      <c r="D66" s="4"/>
-      <c r="E66" s="36"/>
+      <c r="B66" s="37" t="s">
+        <v>108</v>
+      </c>
+      <c r="C66" s="45" t="s">
+        <v>106</v>
+      </c>
+      <c r="D66" s="5"/>
+      <c r="E66" s="35" t="s">
+        <v>109</v>
+      </c>
       <c r="F66" s="1"/>
       <c r="G66" s="1"/>
       <c r="H66" s="1"/>
@@ -2187,50 +2276,23 @@
     </row>
     <row r="67" ht="15.75" customHeight="1">
       <c r="A67" s="2"/>
-      <c r="B67" s="39" t="s">
-        <v>99</v>
-      </c>
-      <c r="C67" s="47" t="s">
-        <v>100</v>
+      <c r="B67" s="37" t="s">
+        <v>110</v>
+      </c>
+      <c r="C67" s="45" t="s">
+        <v>111</v>
       </c>
       <c r="D67" s="5"/>
-      <c r="E67" s="37" t="s">
-        <v>101</v>
-      </c>
-      <c r="F67" s="1"/>
-      <c r="G67" s="1"/>
-      <c r="H67" s="1"/>
-      <c r="I67" s="1"/>
-      <c r="J67" s="1"/>
-      <c r="K67" s="1"/>
-      <c r="L67" s="1"/>
-      <c r="M67" s="1"/>
-      <c r="N67" s="1"/>
-      <c r="O67" s="1"/>
-      <c r="P67" s="1"/>
-      <c r="Q67" s="1"/>
-      <c r="R67" s="1"/>
-      <c r="S67" s="1"/>
-      <c r="T67" s="1"/>
-      <c r="U67" s="1"/>
-      <c r="V67" s="1"/>
-      <c r="W67" s="1"/>
-      <c r="X67" s="1"/>
-      <c r="Y67" s="1"/>
-      <c r="Z67" s="1"/>
+      <c r="E67" s="35" t="s">
+        <v>112</v>
+      </c>
     </row>
     <row r="68" ht="15.75" customHeight="1">
       <c r="A68" s="2"/>
-      <c r="B68" s="39" t="s">
-        <v>102</v>
-      </c>
-      <c r="C68" s="47" t="s">
-        <v>100</v>
-      </c>
-      <c r="D68" s="5"/>
-      <c r="E68" s="49" t="s">
-        <v>103</v>
-      </c>
+      <c r="B68" s="46"/>
+      <c r="C68" s="47"/>
+      <c r="D68" s="47"/>
+      <c r="E68" s="48"/>
       <c r="F68" s="1"/>
       <c r="G68" s="1"/>
       <c r="H68" s="1"/>
@@ -2253,240 +2315,235 @@
       <c r="Y68" s="1"/>
       <c r="Z68" s="1"/>
     </row>
-    <row r="69" ht="15.75" customHeight="1">
+    <row r="69" ht="15.0" customHeight="1">
       <c r="A69" s="2"/>
-      <c r="B69" s="39" t="s">
-        <v>104</v>
-      </c>
-      <c r="C69" s="47" t="s">
-        <v>105</v>
-      </c>
-      <c r="D69" s="5"/>
-      <c r="E69" s="37" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="70" ht="15.75" customHeight="1">
+      <c r="B69" s="1"/>
+      <c r="C69" s="1"/>
+      <c r="D69" s="1"/>
+      <c r="E69" s="1"/>
+    </row>
+    <row r="70" ht="15.0" customHeight="1">
       <c r="A70" s="2"/>
-      <c r="B70" s="50"/>
-      <c r="C70" s="51"/>
-      <c r="D70" s="51"/>
-      <c r="E70" s="52"/>
-      <c r="F70" s="1"/>
-      <c r="G70" s="1"/>
-      <c r="H70" s="1"/>
-      <c r="I70" s="1"/>
-      <c r="J70" s="1"/>
-      <c r="K70" s="1"/>
-      <c r="L70" s="1"/>
-      <c r="M70" s="1"/>
-      <c r="N70" s="1"/>
-      <c r="O70" s="1"/>
-      <c r="P70" s="1"/>
-      <c r="Q70" s="1"/>
-      <c r="R70" s="1"/>
-      <c r="S70" s="1"/>
-      <c r="T70" s="1"/>
-      <c r="U70" s="1"/>
-      <c r="V70" s="1"/>
-      <c r="W70" s="1"/>
-      <c r="X70" s="1"/>
-      <c r="Y70" s="1"/>
-      <c r="Z70" s="1"/>
+      <c r="B70" s="49" t="s">
+        <v>113</v>
+      </c>
+      <c r="C70" s="4"/>
+      <c r="D70" s="4"/>
+      <c r="E70" s="5"/>
     </row>
     <row r="71" ht="15.0" customHeight="1">
       <c r="A71" s="2"/>
-      <c r="B71" s="1"/>
-      <c r="C71" s="1"/>
-      <c r="D71" s="1"/>
-      <c r="E71" s="1"/>
-    </row>
-    <row r="72" ht="15.0" customHeight="1">
+      <c r="B71" s="32" t="s">
+        <v>25</v>
+      </c>
+      <c r="C71" s="33" t="s">
+        <v>77</v>
+      </c>
+      <c r="D71" s="5"/>
+      <c r="E71" s="50" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="72" ht="24.75" customHeight="1">
       <c r="A72" s="2"/>
-      <c r="B72" s="53" t="s">
-        <v>107</v>
+      <c r="B72" s="40" t="s">
+        <v>114</v>
       </c>
       <c r="C72" s="4"/>
       <c r="D72" s="4"/>
-      <c r="E72" s="5"/>
-    </row>
-    <row r="73" ht="15.0" customHeight="1">
+      <c r="E72" s="4"/>
+    </row>
+    <row r="73" ht="34.5" customHeight="1">
       <c r="A73" s="2"/>
-      <c r="B73" s="33" t="s">
-        <v>23</v>
-      </c>
-      <c r="C73" s="34" t="s">
-        <v>71</v>
+      <c r="B73" s="35" t="s">
+        <v>115</v>
+      </c>
+      <c r="C73" s="45" t="s">
+        <v>116</v>
       </c>
       <c r="D73" s="5"/>
-      <c r="E73" s="33" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="74" ht="24.75" customHeight="1">
+      <c r="E73" s="51" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="74" ht="35.25" customHeight="1">
       <c r="A74" s="2"/>
-      <c r="B74" s="40" t="s">
-        <v>109</v>
-      </c>
-      <c r="C74" s="4"/>
-      <c r="D74" s="4"/>
-      <c r="E74" s="36"/>
-    </row>
-    <row r="75" ht="15.75" customHeight="1">
+      <c r="B74" s="35" t="s">
+        <v>118</v>
+      </c>
+      <c r="C74" s="45" t="s">
+        <v>116</v>
+      </c>
+      <c r="D74" s="5"/>
+      <c r="E74" s="52" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="75" ht="26.25" customHeight="1">
       <c r="A75" s="2"/>
-      <c r="B75" s="37" t="s">
-        <v>110</v>
-      </c>
-      <c r="C75" s="47" t="s">
-        <v>111</v>
+      <c r="B75" s="51" t="s">
+        <v>120</v>
+      </c>
+      <c r="C75" s="45" t="s">
+        <v>116</v>
       </c>
       <c r="D75" s="5"/>
-      <c r="E75" s="54" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="76" ht="15.75" customHeight="1">
+      <c r="E75" s="51" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="76" ht="24.75" customHeight="1">
       <c r="A76" s="2"/>
-      <c r="B76" s="49" t="s">
-        <v>113</v>
-      </c>
-      <c r="C76" s="47" t="s">
-        <v>111</v>
-      </c>
-      <c r="D76" s="5"/>
-      <c r="E76" s="55" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="77" ht="22.5" customHeight="1">
+      <c r="B76" s="40" t="s">
+        <v>122</v>
+      </c>
+      <c r="C76" s="4"/>
+      <c r="D76" s="4"/>
+      <c r="E76" s="4"/>
+    </row>
+    <row r="77" ht="63.75" customHeight="1">
       <c r="A77" s="2"/>
-      <c r="B77" s="54" t="s">
-        <v>115</v>
-      </c>
-      <c r="C77" s="47" t="s">
-        <v>111</v>
+      <c r="B77" s="51" t="s">
+        <v>123</v>
+      </c>
+      <c r="C77" s="45" t="s">
+        <v>124</v>
       </c>
       <c r="D77" s="5"/>
-      <c r="E77" s="54" t="s">
-        <v>116</v>
+      <c r="E77" s="51" t="s">
+        <v>125</v>
       </c>
     </row>
     <row r="78" ht="24.75" customHeight="1">
       <c r="A78" s="2"/>
       <c r="B78" s="40" t="s">
-        <v>117</v>
+        <v>37</v>
       </c>
       <c r="C78" s="4"/>
       <c r="D78" s="4"/>
-      <c r="E78" s="36"/>
-    </row>
-    <row r="79" ht="63.75" customHeight="1">
+      <c r="E78" s="4"/>
+    </row>
+    <row r="79" ht="40.5" customHeight="1">
       <c r="A79" s="2"/>
-      <c r="B79" s="54" t="s">
-        <v>118</v>
-      </c>
-      <c r="C79" s="47" t="s">
-        <v>119</v>
+      <c r="B79" s="52" t="s">
+        <v>126</v>
+      </c>
+      <c r="C79" s="45" t="s">
+        <v>127</v>
       </c>
       <c r="D79" s="5"/>
-      <c r="E79" s="54" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="80" ht="24.75" customHeight="1">
+      <c r="E79" s="52" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="80" ht="32.25" customHeight="1">
       <c r="A80" s="2"/>
-      <c r="B80" s="40" t="s">
-        <v>35</v>
-      </c>
-      <c r="C80" s="4"/>
-      <c r="D80" s="4"/>
-      <c r="E80" s="36"/>
-    </row>
-    <row r="81" ht="20.25" customHeight="1">
+      <c r="B80" s="52" t="s">
+        <v>129</v>
+      </c>
+      <c r="C80" s="45" t="s">
+        <v>127</v>
+      </c>
+      <c r="D80" s="5"/>
+      <c r="E80" s="52" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="81" ht="45.0" customHeight="1">
       <c r="A81" s="2"/>
-      <c r="B81" s="54" t="s">
-        <v>121</v>
-      </c>
-      <c r="C81" s="47" t="s">
-        <v>122</v>
+      <c r="B81" s="52" t="s">
+        <v>131</v>
+      </c>
+      <c r="C81" s="45" t="s">
+        <v>127</v>
       </c>
       <c r="D81" s="5"/>
-      <c r="E81" s="54" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="82" ht="15.75" customHeight="1">
+      <c r="E81" s="52" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="82" ht="30.0" customHeight="1">
       <c r="A82" s="2"/>
-      <c r="B82" s="54" t="s">
-        <v>124</v>
-      </c>
-      <c r="C82" s="47" t="s">
-        <v>122</v>
+      <c r="B82" s="52" t="s">
+        <v>133</v>
+      </c>
+      <c r="C82" s="45" t="s">
+        <v>127</v>
       </c>
       <c r="D82" s="5"/>
-      <c r="E82" s="54" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="83" ht="24.75" customHeight="1">
+      <c r="E82" s="52" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="83" ht="31.5" customHeight="1">
       <c r="A83" s="2"/>
-      <c r="B83" s="40" t="s">
-        <v>126</v>
-      </c>
-      <c r="C83" s="4"/>
-      <c r="D83" s="4"/>
-      <c r="E83" s="36"/>
-    </row>
-    <row r="84" ht="15.75" customHeight="1">
+      <c r="B83" s="52" t="s">
+        <v>135</v>
+      </c>
+      <c r="C83" s="45" t="s">
+        <v>127</v>
+      </c>
+      <c r="D83" s="5"/>
+      <c r="E83" s="52" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="84" ht="24.75" customHeight="1">
       <c r="A84" s="2"/>
-      <c r="B84" s="54" t="s">
-        <v>127</v>
-      </c>
-      <c r="C84" s="47" t="s">
-        <v>128</v>
-      </c>
-      <c r="D84" s="5"/>
-      <c r="E84" s="54" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="85" ht="15.75" customHeight="1">
+      <c r="B84" s="40" t="s">
+        <v>137</v>
+      </c>
+      <c r="C84" s="4"/>
+      <c r="D84" s="4"/>
+      <c r="E84" s="4"/>
+    </row>
+    <row r="85" ht="31.5" customHeight="1">
       <c r="A85" s="2"/>
-      <c r="B85" s="54" t="s">
-        <v>130</v>
-      </c>
-      <c r="C85" s="47" t="s">
-        <v>128</v>
+      <c r="B85" s="52" t="s">
+        <v>138</v>
+      </c>
+      <c r="C85" s="45" t="s">
+        <v>139</v>
       </c>
       <c r="D85" s="5"/>
-      <c r="E85" s="54" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="86" ht="24.75" customHeight="1">
+      <c r="E85" s="51" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="86" ht="27.0" customHeight="1">
       <c r="A86" s="2"/>
-      <c r="B86" s="40" t="s">
-        <v>98</v>
-      </c>
-      <c r="C86" s="4"/>
-      <c r="D86" s="4"/>
-      <c r="E86" s="36"/>
-    </row>
-    <row r="87" ht="15.75" customHeight="1">
+      <c r="B86" s="52" t="s">
+        <v>141</v>
+      </c>
+      <c r="C86" s="45" t="s">
+        <v>139</v>
+      </c>
+      <c r="D86" s="5"/>
+      <c r="E86" s="51" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="87" ht="24.75" customHeight="1">
       <c r="A87" s="2"/>
-      <c r="B87" s="55" t="s">
-        <v>132</v>
-      </c>
-      <c r="C87" s="47" t="s">
-        <v>133</v>
-      </c>
-      <c r="D87" s="5"/>
-      <c r="E87" s="54" t="s">
-        <v>134</v>
-      </c>
+      <c r="B87" s="40" t="s">
+        <v>104</v>
+      </c>
+      <c r="C87" s="4"/>
+      <c r="D87" s="4"/>
+      <c r="E87" s="4"/>
     </row>
     <row r="88" ht="15.75" customHeight="1">
       <c r="A88" s="2"/>
+      <c r="B88" s="52" t="s">
+        <v>143</v>
+      </c>
+      <c r="C88" s="45" t="s">
+        <v>144</v>
+      </c>
+      <c r="D88" s="5"/>
+      <c r="E88" s="51" t="s">
+        <v>145</v>
+      </c>
     </row>
     <row r="89" ht="15.75" customHeight="1">
       <c r="A89" s="2"/>
@@ -2650,7 +2707,9 @@
     <row r="142" ht="15.75" customHeight="1">
       <c r="A142" s="2"/>
     </row>
-    <row r="143" ht="15.75" customHeight="1"/>
+    <row r="143" ht="15.75" customHeight="1">
+      <c r="A143" s="2"/>
+    </row>
     <row r="144" ht="15.75" customHeight="1"/>
     <row r="145" ht="15.75" customHeight="1"/>
     <row r="146" ht="15.75" customHeight="1"/>
@@ -3507,75 +3566,82 @@
     <row r="997" ht="15.75" customHeight="1"/>
     <row r="998" ht="15.75" customHeight="1"/>
     <row r="999" ht="15.75" customHeight="1"/>
+    <row r="1000" ht="15.75" customHeight="1"/>
+    <row r="1001" ht="15.75" customHeight="1"/>
   </sheetData>
-  <mergeCells count="67">
-    <mergeCell ref="C69:D69"/>
+  <mergeCells count="72">
+    <mergeCell ref="C66:D66"/>
+    <mergeCell ref="C67:D67"/>
+    <mergeCell ref="B70:E70"/>
+    <mergeCell ref="C71:D71"/>
     <mergeCell ref="B72:E72"/>
     <mergeCell ref="C73:D73"/>
-    <mergeCell ref="B74:E74"/>
+    <mergeCell ref="C74:D74"/>
+    <mergeCell ref="C85:D85"/>
+    <mergeCell ref="C86:D86"/>
+    <mergeCell ref="B87:E87"/>
+    <mergeCell ref="C88:D88"/>
+    <mergeCell ref="C79:D79"/>
+    <mergeCell ref="C81:D81"/>
+    <mergeCell ref="C80:D80"/>
     <mergeCell ref="C75:D75"/>
-    <mergeCell ref="C76:D76"/>
+    <mergeCell ref="B76:E76"/>
     <mergeCell ref="C77:D77"/>
-    <mergeCell ref="C85:D85"/>
-    <mergeCell ref="B86:E86"/>
-    <mergeCell ref="C87:D87"/>
     <mergeCell ref="B78:E78"/>
-    <mergeCell ref="C79:D79"/>
-    <mergeCell ref="B80:E80"/>
-    <mergeCell ref="C81:D81"/>
     <mergeCell ref="C82:D82"/>
-    <mergeCell ref="B83:E83"/>
-    <mergeCell ref="C84:D84"/>
+    <mergeCell ref="C83:D83"/>
+    <mergeCell ref="B84:E84"/>
     <mergeCell ref="B2:E2"/>
     <mergeCell ref="D3:D6"/>
     <mergeCell ref="E3:E6"/>
     <mergeCell ref="B9:E9"/>
-    <mergeCell ref="B22:E22"/>
-    <mergeCell ref="B23:E23"/>
+    <mergeCell ref="B18:E18"/>
+    <mergeCell ref="B19:E19"/>
+    <mergeCell ref="C20:D20"/>
+    <mergeCell ref="B21:E21"/>
+    <mergeCell ref="C22:D22"/>
+    <mergeCell ref="C23:D23"/>
     <mergeCell ref="C24:D24"/>
-    <mergeCell ref="B25:E25"/>
-    <mergeCell ref="C26:D26"/>
+    <mergeCell ref="C25:D25"/>
+    <mergeCell ref="B26:E26"/>
+    <mergeCell ref="C28:D28"/>
     <mergeCell ref="C27:D27"/>
-    <mergeCell ref="C28:D28"/>
     <mergeCell ref="C29:D29"/>
-    <mergeCell ref="B30:E30"/>
+    <mergeCell ref="C30:D30"/>
     <mergeCell ref="C31:D31"/>
     <mergeCell ref="C32:D32"/>
     <mergeCell ref="C33:D33"/>
     <mergeCell ref="C34:D34"/>
     <mergeCell ref="C35:D35"/>
-    <mergeCell ref="C36:D36"/>
+    <mergeCell ref="B36:E36"/>
     <mergeCell ref="C37:D37"/>
     <mergeCell ref="C38:D38"/>
-    <mergeCell ref="B39:E39"/>
-    <mergeCell ref="C40:D40"/>
+    <mergeCell ref="C39:D39"/>
+    <mergeCell ref="B40:E40"/>
     <mergeCell ref="C41:D41"/>
     <mergeCell ref="C42:D42"/>
-    <mergeCell ref="B43:E43"/>
+    <mergeCell ref="C43:D43"/>
     <mergeCell ref="C44:D44"/>
     <mergeCell ref="C45:D45"/>
-    <mergeCell ref="C46:D46"/>
-    <mergeCell ref="C47:D47"/>
+    <mergeCell ref="B48:E48"/>
+    <mergeCell ref="C49:D49"/>
     <mergeCell ref="B50:E50"/>
     <mergeCell ref="C51:D51"/>
-    <mergeCell ref="B52:E52"/>
+    <mergeCell ref="C46:D46"/>
+    <mergeCell ref="C52:D52"/>
     <mergeCell ref="C53:D53"/>
-    <mergeCell ref="C54:D54"/>
-    <mergeCell ref="C48:D48"/>
+    <mergeCell ref="B54:E54"/>
     <mergeCell ref="C55:D55"/>
-    <mergeCell ref="B56:E56"/>
+    <mergeCell ref="C56:D56"/>
     <mergeCell ref="C57:D57"/>
-    <mergeCell ref="C58:D58"/>
+    <mergeCell ref="B58:E58"/>
     <mergeCell ref="C59:D59"/>
-    <mergeCell ref="B60:E60"/>
-    <mergeCell ref="C61:D61"/>
+    <mergeCell ref="C60:D60"/>
+    <mergeCell ref="B61:E61"/>
     <mergeCell ref="C62:D62"/>
-    <mergeCell ref="B63:E63"/>
-    <mergeCell ref="C64:D64"/>
+    <mergeCell ref="C63:D63"/>
+    <mergeCell ref="B64:E64"/>
     <mergeCell ref="C65:D65"/>
-    <mergeCell ref="B66:E66"/>
-    <mergeCell ref="C67:D67"/>
-    <mergeCell ref="C68:D68"/>
   </mergeCells>
   <printOptions/>
   <pageMargins bottom="0.75" footer="0.0" header="0.0" left="0.7" right="0.7" top="0.75"/>
